--- a/manufacturing/BOM/BOM_AFC_v4-0-5_DUNE_Newbury_F4578-REV3_20260909101506.xlsx
+++ b/manufacturing/BOM/BOM_AFC_v4-0-5_DUNE_Newbury_F4578-REV3_20260909101506.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phdgc\Downloads\DUNE-Variant-AMC-FMC-Carrier-AFC\manufacturing\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBA8A02-9E41-4BF4-8251-B7D296718424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-900" yWindow="-17235" windowWidth="39705" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="602">
   <si>
     <t>Description</t>
   </si>
@@ -62,9 +67,6 @@
     <t>710-885012208019</t>
   </si>
   <si>
-    <t>C1A, C1B, C5A, C5B, C7A, C7B, C46, C47, C66, C68, C79, C81, C85, C87, C116, C117, C119, C122, C123, C136, C137, C139, C142, C154, C155, C156, C157, C158, C161, C162, C163, C164, C165, C168, C169, C170, C171, C172, C173, C174, C175, C176, C177, C454, C462, C464, C471, C472, C474, C477, C529, C530, C531, C534, C540, C541, C542, C544, C545, C546</t>
-  </si>
-  <si>
     <t>Cut Tape</t>
   </si>
   <si>
@@ -1068,9 +1070,6 @@
   </si>
   <si>
     <t>SRN3015-1R0Y</t>
-  </si>
-  <si>
-    <t>L2, L4, L7</t>
   </si>
   <si>
     <t>FIXED IND 440NH 30A 0.32 MOHM</t>
@@ -1824,31 +1823,36 @@
   </si>
   <si>
     <t>XTAL_32.768KHZ_ABRACON_ABS25-32.768KHZ-T</t>
+  </si>
+  <si>
+    <t>L2, L4, L7,L9</t>
+  </si>
+  <si>
+    <t>C1A, C1B, C5A, C5B, C7A, C7B, C46, C47, C66, C68, C79, C81, C85, C87, C116, C117, C119, C122, C123, C136, C137, C139, C142, C154, C155, C156, C157, C158, C161, C162, C163, C164, C165, C168, C169, C170, C171, C172, C173, C174, C175, C176, C177, C454, C455a, C455b, C462, C464, C471, C472, C474, C477, C529, C530, C531, C534, C540, C541, C542, C544, C545, C546</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1886,23 +1890,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2192,30 +2207,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N133"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="125" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10" customWidth="true" style="0"/>
-    <col min="3" max="3" width="12" customWidth="true" style="0"/>
-    <col min="4" max="4" width="20" customWidth="true" style="0"/>
-    <col min="5" max="5" width="28" customWidth="true" style="0"/>
-    <col min="6" max="6" width="44" customWidth="true" style="0"/>
-    <col min="7" max="7" width="15" customWidth="true" style="0"/>
-    <col min="8" max="8" width="30" customWidth="true" style="0"/>
-    <col min="9" max="9" width="50" customWidth="true" style="0"/>
-    <col min="10" max="10" width="20" customWidth="true" style="0"/>
-    <col min="11" max="11" width="16" customWidth="true" style="0"/>
-    <col min="12" max="12" width="50" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15" customWidth="true" style="0"/>
-    <col min="14" max="14" width="44" customWidth="true" style="0"/>
+    <col min="1" max="1" width="125" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="50" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" customHeight="1" ht="40">
+    <row r="1" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2250,27 +2262,27 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" customHeight="1" ht="86">
+    </row>
+    <row r="2" spans="1:14" ht="86" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3">
-        <v>2640</v>
+        <v>2728</v>
       </c>
       <c r="D2" s="3">
-        <v>2640</v>
+        <v>2728</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>12</v>
@@ -2284,28 +2296,28 @@
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N2" s="3">
         <v>885012208019</v>
       </c>
     </row>
-    <row r="3" spans="1:14" customHeight="1" ht="74">
+    <row r="3" spans="1:14" ht="74" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3">
         <v>53</v>
@@ -2317,39 +2329,39 @@
         <v>2332</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="409.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" customHeight="1" ht="459.75">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="B4" s="3">
         <v>314</v>
@@ -2361,39 +2373,39 @@
         <v>13816</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="40.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" customHeight="1" ht="40.25">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>29</v>
@@ -2405,39 +2417,39 @@
         <v>1276</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" customHeight="1" ht="15">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -2449,39 +2461,39 @@
         <v>88</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" customHeight="1" ht="15">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
@@ -2493,39 +2505,39 @@
         <v>352</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" customHeight="1" ht="15">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
@@ -2537,39 +2549,39 @@
         <v>440</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" customHeight="1" ht="15">
-      <c r="A9" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>7</v>
@@ -2581,39 +2593,39 @@
         <v>308</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="88" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" customHeight="1" ht="88">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="B10" s="3">
         <v>59</v>
@@ -2625,39 +2637,39 @@
         <v>2596</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" customHeight="1" ht="15">
-      <c r="A11" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -2669,39 +2681,39 @@
         <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="H11" s="3">
         <v>3783058</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" customHeight="1" ht="15">
-      <c r="A12" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="B12" s="3">
         <v>3</v>
@@ -2713,39 +2725,39 @@
         <v>132</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" customHeight="1" ht="15">
-      <c r="A13" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -2757,39 +2769,39 @@
         <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" customHeight="1" ht="23.5">
-      <c r="A14" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="B14" s="3">
         <v>16</v>
@@ -2801,39 +2813,39 @@
         <v>704</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="3">
         <v>1108328</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="106" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" customHeight="1" ht="106">
-      <c r="A15" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="B15" s="3">
         <v>71</v>
@@ -2845,39 +2857,39 @@
         <v>3124</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="3">
         <v>2112845</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" customHeight="1" ht="23.5">
-      <c r="A16" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="B16" s="3">
         <v>16</v>
@@ -2889,39 +2901,39 @@
         <v>704</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="91" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" customHeight="1" ht="91">
-      <c r="A17" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="B17" s="3">
         <v>61</v>
@@ -2933,39 +2945,39 @@
         <v>2684</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" customHeight="1" ht="15">
-      <c r="A18" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -2977,39 +2989,39 @@
         <v>88</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3">
         <v>4936484</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" customHeight="1" ht="15">
-      <c r="A19" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -3021,37 +3033,37 @@
         <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" customHeight="1" ht="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3">
         <v>2</v>
@@ -3063,39 +3075,39 @@
         <v>88</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H20" s="3">
         <v>4922032</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" customHeight="1" ht="15">
-      <c r="A21" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -3107,39 +3119,39 @@
         <v>44</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" customHeight="1" ht="15">
-      <c r="A22" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -3151,39 +3163,39 @@
         <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H22" s="3">
         <v>1327634</v>
       </c>
       <c r="I22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" customHeight="1" ht="15">
-      <c r="A23" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -3195,39 +3207,39 @@
         <v>88</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" customHeight="1" ht="15">
-      <c r="A24" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -3239,39 +3251,39 @@
         <v>44</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" customHeight="1" ht="15">
-      <c r="A25" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -3283,39 +3295,39 @@
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" customHeight="1" ht="15">
-      <c r="A26" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
@@ -3327,37 +3339,37 @@
         <v>88</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H26" s="3">
         <v>2101190</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" customHeight="1" ht="16">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>14</v>
@@ -3369,39 +3381,39 @@
         <v>616</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" customHeight="1" ht="15">
-      <c r="A28" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -3413,37 +3425,37 @@
         <v>44</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H28" s="3">
         <v>1299276</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" customHeight="1" ht="15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B29" s="3">
         <v>10</v>
@@ -3455,37 +3467,37 @@
         <v>440</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" customHeight="1" ht="15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B30" s="3">
         <v>2</v>
@@ -3497,37 +3509,37 @@
         <v>88</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" customHeight="1" ht="15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
@@ -3539,37 +3551,37 @@
         <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H31" s="3">
         <v>1295310</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" customHeight="1" ht="15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B32" s="3">
         <v>3</v>
@@ -3581,37 +3593,37 @@
         <v>132</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" customHeight="1" ht="15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="3">
         <v>1</v>
@@ -3623,37 +3635,37 @@
         <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H33" s="3">
         <v>2250006</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" customHeight="1" ht="15">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" s="3">
         <v>5</v>
@@ -3665,37 +3677,37 @@
         <v>220</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H34" s="3" t="s">
+      <c r="I34" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" customHeight="1" ht="15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="3">
         <v>2</v>
@@ -3707,37 +3719,37 @@
         <v>88</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="I35" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" customHeight="1" ht="15">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3">
         <v>4</v>
@@ -3749,37 +3761,37 @@
         <v>176</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H36" s="3">
         <v>9526900</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" customHeight="1" ht="15">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
@@ -3791,37 +3803,37 @@
         <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="H37" s="3">
         <v>6084001</v>
       </c>
       <c r="I37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="K37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" customHeight="1" ht="15">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
@@ -3833,35 +3845,35 @@
         <v>44</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" customHeight="1" ht="15">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
@@ -3873,39 +3885,39 @@
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="I39" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" customHeight="1" ht="15">
-      <c r="A40" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -3917,37 +3929,37 @@
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="J40" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="K40" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" customHeight="1" ht="15">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B41" s="3">
         <v>1</v>
@@ -3959,35 +3971,35 @@
         <v>44</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" customHeight="1" ht="15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
@@ -3999,39 +4011,39 @@
         <v>88</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42" s="3">
         <v>8735077</v>
       </c>
       <c r="I42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" customHeight="1" ht="15">
-      <c r="A43" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="B43" s="3">
         <v>3</v>
@@ -4043,37 +4055,37 @@
         <v>132</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H43" s="3" t="s">
+      <c r="I43" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" customHeight="1" ht="15">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B44" s="3">
         <v>3</v>
@@ -4085,37 +4097,37 @@
         <v>132</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" customHeight="1" ht="15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3">
         <v>1</v>
@@ -4127,37 +4139,37 @@
         <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H45" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="J45" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K45" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" customHeight="1" ht="15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
@@ -4169,37 +4181,37 @@
         <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H46" s="3">
         <v>3120987</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" customHeight="1" ht="15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
@@ -4211,37 +4223,37 @@
         <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" customHeight="1" ht="15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B48" s="3">
         <v>6</v>
@@ -4253,37 +4265,37 @@
         <v>264</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F48" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" customHeight="1" ht="15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3">
         <v>1</v>
@@ -4295,37 +4307,37 @@
         <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H49" s="3">
         <v>2515695</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" customHeight="1" ht="15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
@@ -4337,37 +4349,37 @@
         <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H50" s="3" t="s">
+      <c r="I50" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" customHeight="1" ht="15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B51" s="3">
         <v>6</v>
@@ -4379,37 +4391,37 @@
         <v>264</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" customHeight="1" ht="15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B52" s="3">
         <v>3</v>
@@ -4421,37 +4433,37 @@
         <v>132</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H52" s="3">
         <v>3124701</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" customHeight="1" ht="15">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" s="3">
         <v>2</v>
@@ -4463,37 +4475,37 @@
         <v>88</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H53" s="3" t="s">
+      <c r="I53" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" customHeight="1" ht="15">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
@@ -4505,37 +4517,37 @@
         <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" customHeight="1" ht="15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B55" s="3">
         <v>4</v>
@@ -4547,37 +4559,37 @@
         <v>176</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" customHeight="1" ht="15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -4589,37 +4601,37 @@
         <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H56" s="3">
         <v>3123126</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" customHeight="1" ht="15">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
@@ -4631,37 +4643,37 @@
         <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H57" s="3" t="s">
+      <c r="I57" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="J57" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" customHeight="1" ht="15">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
@@ -4673,37 +4685,37 @@
         <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I58" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" customHeight="1" ht="15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
@@ -4715,37 +4727,37 @@
         <v>44</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F59" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H59" s="3" t="s">
+      <c r="I59" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" customHeight="1" ht="15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B60" s="3">
         <v>1</v>
@@ -4757,37 +4769,37 @@
         <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="G60" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H60" s="3">
         <v>2564478</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" customHeight="1" ht="15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B61" s="3">
         <v>3</v>
@@ -4799,37 +4811,37 @@
         <v>132</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H61" s="3">
         <v>1467314</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" customHeight="1" ht="15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B62" s="3">
         <v>1</v>
@@ -4841,37 +4853,37 @@
         <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H62" s="3">
         <v>333195001</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" customHeight="1" ht="15">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
@@ -4883,37 +4895,37 @@
         <v>44</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F63" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H63" s="3" t="s">
+      <c r="I63" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="J63" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="K63" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" customHeight="1" ht="15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B64" s="3">
         <v>2</v>
@@ -4925,37 +4937,37 @@
         <v>88</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F64" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H64" s="3" t="s">
+      <c r="I64" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="J64" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" customHeight="1" ht="15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B65" s="3">
         <v>1</v>
@@ -4967,37 +4979,37 @@
         <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="G65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H65" s="3" t="s">
+      <c r="I65" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="J65" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" customHeight="1" ht="15">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
@@ -5009,37 +5021,37 @@
         <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H66" s="3" t="s">
+      <c r="I66" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>291</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" customHeight="1" ht="15">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
@@ -5051,37 +5063,37 @@
         <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F67" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H67" s="3" t="s">
+      <c r="I67" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="J67" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" customHeight="1" ht="15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
@@ -5093,37 +5105,37 @@
         <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H68" s="3">
         <v>2296040</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" customHeight="1" ht="15">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B69" s="3">
         <v>1</v>
@@ -5135,37 +5147,37 @@
         <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="G69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H69" s="3" t="s">
+      <c r="I69" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="J69" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" customHeight="1" ht="15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B70" s="3">
         <v>11</v>
@@ -5177,37 +5189,37 @@
         <v>484</v>
       </c>
       <c r="E70" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="G70" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H70" s="3">
         <v>1688077</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" customHeight="1" ht="15">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
@@ -5219,37 +5231,37 @@
         <v>44</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F71" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="I71" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="J71" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="K71" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" customHeight="1" ht="15">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B72" s="3">
         <v>1</v>
@@ -5261,39 +5273,39 @@
         <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="G72" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H72" s="3">
         <v>1323260001</v>
       </c>
       <c r="I72" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" customHeight="1" ht="15">
-      <c r="A73" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="B73" s="3">
         <v>1</v>
@@ -5305,37 +5317,37 @@
         <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="G73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="J73" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" customHeight="1" ht="15">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B74" s="3">
         <v>1</v>
@@ -5347,37 +5359,37 @@
         <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="G74" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="J74" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" customHeight="1" ht="15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B75" s="3">
         <v>2</v>
@@ -5389,37 +5401,37 @@
         <v>88</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F75" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="I75" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" customHeight="1" ht="15">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
@@ -5431,37 +5443,37 @@
         <v>44</v>
       </c>
       <c r="E76" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="G76" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H76" s="3">
         <v>3550949</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" customHeight="1" ht="15">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
@@ -5473,37 +5485,37 @@
         <v>44</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F77" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="J77" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" customHeight="1" ht="15">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B78" s="3">
         <v>1</v>
@@ -5515,37 +5527,37 @@
         <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F78" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="J78" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" customHeight="1" ht="15">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B79" s="3">
         <v>6</v>
@@ -5557,79 +5569,79 @@
         <v>264</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H79" s="3">
         <v>2706200</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" customHeight="1" ht="15">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B80" s="3">
+        <v>4</v>
+      </c>
+      <c r="C80" s="3">
+        <v>176</v>
+      </c>
+      <c r="D80" s="3">
+        <v>176</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B80" s="3">
-        <v>3</v>
-      </c>
-      <c r="C80" s="3">
-        <v>132</v>
-      </c>
-      <c r="D80" s="3">
-        <v>132</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="G80" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H80" s="3">
         <v>4216466</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>351</v>
+      <c r="I80" s="4" t="s">
+        <v>600</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N80" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
         <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" customHeight="1" ht="15">
-      <c r="A81" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
@@ -5641,37 +5653,37 @@
         <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="J81" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" customHeight="1" ht="15">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
@@ -5683,37 +5695,37 @@
         <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="I82" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="J82" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" customHeight="1" ht="15">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
@@ -5725,37 +5737,37 @@
         <v>44</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F83" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="J83" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" customHeight="1" ht="15">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B84" s="3">
         <v>1</v>
@@ -5767,37 +5779,37 @@
         <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H84" s="3">
         <v>1678707</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N84" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" customHeight="1" ht="19.5">
-      <c r="A85" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="B85" s="3">
         <v>12</v>
@@ -5809,37 +5821,37 @@
         <v>528</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H85" s="3">
         <v>2426216</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" customHeight="1" ht="15">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B86" s="3">
         <v>1</v>
@@ -5851,39 +5863,39 @@
         <v>44</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" customHeight="1" ht="15">
-      <c r="A87" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="B87" s="3">
         <v>1</v>
@@ -5895,37 +5907,37 @@
         <v>44</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" customHeight="1" ht="15">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B88" s="3">
         <v>1</v>
@@ -5937,37 +5949,37 @@
         <v>44</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H88" s="3">
         <v>9575154</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N88" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" customHeight="1" ht="15">
-      <c r="A89" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="B89" s="3">
         <v>3</v>
@@ -5979,39 +5991,39 @@
         <v>2500</v>
       </c>
       <c r="E89" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="I89" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="K89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" customHeight="1" ht="17">
-      <c r="A90" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="B90" s="3">
         <v>16</v>
@@ -6023,37 +6035,37 @@
         <v>704</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F90" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I90" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="J90" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" customHeight="1" ht="15">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B91" s="3">
         <v>4</v>
@@ -6065,37 +6077,37 @@
         <v>176</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" customHeight="1" ht="15">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B92" s="3">
         <v>1</v>
@@ -6107,37 +6119,37 @@
         <v>44</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" customHeight="1" ht="15">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B93" s="3">
         <v>1</v>
@@ -6149,35 +6161,35 @@
         <v>44</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H93" s="3">
         <v>2480776</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J93" s="3"/>
       <c r="K93" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" customHeight="1" ht="15">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B94" s="3">
         <v>6</v>
@@ -6189,37 +6201,37 @@
         <v>264</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" customHeight="1" ht="89.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B95" s="3">
         <v>61</v>
@@ -6231,39 +6243,39 @@
         <v>2684</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H95" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="194.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" customHeight="1" ht="194.25">
-      <c r="A96" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="B96" s="3">
         <v>137</v>
@@ -6275,39 +6287,39 @@
         <v>6028</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H96" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" customHeight="1" ht="22.5">
-      <c r="A97" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="B97" s="3">
         <v>18</v>
@@ -6319,39 +6331,39 @@
         <v>792</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H97" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N97" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" customHeight="1" ht="15">
-      <c r="A98" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="B98" s="3">
         <v>11</v>
@@ -6363,39 +6375,39 @@
         <v>484</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H98" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" customHeight="1" ht="26">
-      <c r="A99" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="B99" s="3">
         <v>18</v>
@@ -6407,39 +6419,39 @@
         <v>792</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H99" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J99" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" customHeight="1" ht="15.75">
-      <c r="A100" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="B100" s="3">
         <v>12</v>
@@ -6451,39 +6463,39 @@
         <v>528</v>
       </c>
       <c r="E100" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="I100" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="J100" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" customHeight="1" ht="26.75">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="26.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B101" s="3">
         <v>6</v>
@@ -6495,39 +6507,39 @@
         <v>264</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" customHeight="1" ht="15">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B102" s="3">
         <v>3</v>
@@ -6539,39 +6551,39 @@
         <v>132</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H102" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" customHeight="1" ht="28.5">
-      <c r="A103" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="B103" s="3">
         <v>20</v>
@@ -6583,39 +6595,39 @@
         <v>880</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H103" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N103" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" customHeight="1" ht="15">
-      <c r="A104" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="B104" s="3">
         <v>1</v>
@@ -6627,39 +6639,39 @@
         <v>5000</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H104" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="I104" s="2" t="s">
+      <c r="K104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N104" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K104" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M104" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" customHeight="1" ht="15">
-      <c r="A105" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="B105" s="3">
         <v>10</v>
@@ -6671,39 +6683,39 @@
         <v>440</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H105" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M105" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" customHeight="1" ht="15">
-      <c r="A106" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="B106" s="3">
         <v>3</v>
@@ -6715,39 +6727,39 @@
         <v>132</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="I106" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H106" s="3" t="s">
+      <c r="J106" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N106" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K106" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M106" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" customHeight="1" ht="15">
-      <c r="A107" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="B107" s="3">
         <v>3</v>
@@ -6759,39 +6771,39 @@
         <v>132</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H107" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M107" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N107" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K107" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M107" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" customHeight="1" ht="15">
-      <c r="A108" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="B108" s="3">
         <v>8</v>
@@ -6803,39 +6815,39 @@
         <v>352</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H108" s="3">
         <v>3952392</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N108" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
         <v>472</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" customHeight="1" ht="15">
-      <c r="A109" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="B109" s="3">
         <v>8</v>
@@ -6847,37 +6859,37 @@
         <v>352</v>
       </c>
       <c r="E109" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H109" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="I109" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="J109" s="3"/>
       <c r="K109" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" customHeight="1" ht="15">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B110" s="3">
         <v>5</v>
@@ -6889,39 +6901,39 @@
         <v>220</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H110" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" customHeight="1" ht="15">
-      <c r="A111" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="B111" s="3">
         <v>1</v>
@@ -6933,39 +6945,39 @@
         <v>44</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F111" s="3">
         <v>560112116063</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H111" s="3">
         <v>4352027</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N111" s="3">
         <v>560112116063</v>
       </c>
     </row>
-    <row r="112" spans="1:14" customHeight="1" ht="15">
+    <row r="112" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B112" s="3">
         <v>3</v>
@@ -6977,39 +6989,39 @@
         <v>132</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H112" s="3">
         <v>4559985</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N112" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
         <v>487</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" customHeight="1" ht="15">
-      <c r="A113" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="B113" s="3">
         <v>1</v>
@@ -7021,39 +7033,39 @@
         <v>44</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F113" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I113" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H113" s="3" t="s">
+      <c r="J113" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" customHeight="1" ht="15">
-      <c r="A114" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="B114" s="3">
         <v>1</v>
@@ -7065,39 +7077,39 @@
         <v>44</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H114" s="3">
         <v>3496239</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N114" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>494</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" customHeight="1" ht="20.5">
-      <c r="A115" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="B115" s="3">
         <v>14</v>
@@ -7109,39 +7121,39 @@
         <v>616</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F115" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="I115" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H115" s="3" t="s">
+      <c r="J115" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M115" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N115" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" customHeight="1" ht="37">
-      <c r="A116" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="B116" s="3">
         <v>25</v>
@@ -7153,39 +7165,39 @@
         <v>1100</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H116" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M116" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" customHeight="1" ht="15">
-      <c r="A117" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="B117" s="3">
         <v>1</v>
@@ -7197,39 +7209,39 @@
         <v>44</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F117" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="I117" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H117" s="3" t="s">
+      <c r="J117" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N117" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J117" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K117" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M117" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N117" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" customHeight="1" ht="15">
-      <c r="A118" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="B118" s="3">
         <v>2</v>
@@ -7241,39 +7253,39 @@
         <v>88</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H118" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M118" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N118" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M118" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N118" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" customHeight="1" ht="15">
-      <c r="A119" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
@@ -7285,39 +7297,39 @@
         <v>88</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H119" s="3">
         <v>1856982</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N119" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
         <v>513</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" customHeight="1" ht="45.75">
-      <c r="A120" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="B120" s="3">
         <v>31</v>
@@ -7329,39 +7341,39 @@
         <v>1364</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H120" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M120" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N120" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M120" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N120" s="3" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14" customHeight="1" ht="37">
-      <c r="A121" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="B121" s="3">
         <v>25</v>
@@ -7373,39 +7385,39 @@
         <v>1100</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H121" s="3">
         <v>4841172</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N121" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
         <v>520</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" customHeight="1" ht="15">
-      <c r="A122" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="B122" s="3">
         <v>1</v>
@@ -7417,39 +7429,39 @@
         <v>44</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H122" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N122" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K122" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M122" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N122" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14" customHeight="1" ht="15">
-      <c r="A123" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="B123" s="3">
         <v>2</v>
@@ -7461,39 +7473,39 @@
         <v>88</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F123" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="I123" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H123" s="3" t="s">
+      <c r="J123" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M123" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N123" s="3" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" customHeight="1" ht="15">
-      <c r="A124" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="B124" s="3">
         <v>2</v>
@@ -7505,39 +7517,39 @@
         <v>88</v>
       </c>
       <c r="E124" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="I124" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H124" s="3" t="s">
+      <c r="J124" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N124" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="17.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="J124" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="M124" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" customHeight="1" ht="17.75">
-      <c r="A125" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="B125" s="3">
         <v>2</v>
@@ -7549,39 +7561,39 @@
         <v>88</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H125" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="M125" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N125" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="J125" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K125" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="M125" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N125" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" customHeight="1" ht="15">
-      <c r="A126" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="B126" s="3">
         <v>1</v>
@@ -7593,39 +7605,39 @@
         <v>44</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H126" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="M126" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N126" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K126" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="M126" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N126" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" customHeight="1" ht="15">
-      <c r="A127" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="B127" s="3">
         <v>1</v>
@@ -7637,39 +7649,39 @@
         <v>44</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H127" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N127" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K127" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="M127" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N127" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" customHeight="1" ht="15">
-      <c r="A128" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="B128" s="3">
         <v>1</v>
@@ -7681,39 +7693,39 @@
         <v>44</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F128" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I128" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H128" s="3" t="s">
+      <c r="J128" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K128" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N128" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14" customHeight="1" ht="15">
-      <c r="A129" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="B129" s="3">
         <v>3</v>
@@ -7725,39 +7737,39 @@
         <v>132</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F129" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="I129" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H129" s="3" t="s">
+      <c r="J129" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="M129" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N129" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L129" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="M129" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N129" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" customHeight="1" ht="15">
-      <c r="A130" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="B130" s="3">
         <v>1</v>
@@ -7769,37 +7781,37 @@
         <v>44</v>
       </c>
       <c r="E130" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="I130" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="J130" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14" customHeight="1" ht="15">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B131" s="3">
         <v>1</v>
@@ -7811,37 +7823,37 @@
         <v>44</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H131" s="3">
         <v>4072544</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N131" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
         <v>563</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14" customHeight="1" ht="15">
-      <c r="A132" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="B132" s="3">
         <v>1</v>
@@ -7853,39 +7865,39 @@
         <v>44</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H132" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="N132" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="J132" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K132" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="M132" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="N132" s="3" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14" customHeight="1" ht="15">
-      <c r="A133" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="B133" s="3">
         <v>1</v>
@@ -7897,46 +7909,35 @@
         <v>44</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>